--- a/ils/MIgrationDecisiontable.xlsx
+++ b/ils/MIgrationDecisiontable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ContainOpenSource\Java\OpenSourceJava\ils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{AA646879-0433-4D5C-8A6A-428A9E6DFF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B22D25-C048-4153-B2DD-B9150BF4455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{38A679BF-43A7-436C-8848-BC58323E04C3}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="38">
   <si>
     <t>SPO</t>
   </si>
@@ -150,6 +149,15 @@
   </si>
   <si>
     <t>documentlibrary/secret</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Checked</t>
+  </si>
+  <si>
+    <t>✓</t>
   </si>
 </sst>
 </file>
@@ -242,12 +250,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -271,6 +273,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,682 +614,805 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F68FC6CF-A2A1-424F-99BE-9E64AEC34370}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="76.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="30.85546875" customWidth="1"/>
-    <col min="7" max="7" width="75.85546875" customWidth="1"/>
-    <col min="8" max="8" width="38" style="2" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="76.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.85546875" customWidth="1"/>
+    <col min="9" max="9" width="75.85546875" customWidth="1"/>
+    <col min="10" max="10" width="38" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="5" t="s">
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="J2" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="2" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="2" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="2" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="J7" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="2" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="J9" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="2" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="2" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="2" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="2" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="2" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>13</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="2" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="2" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="2" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>16</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="2" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>17</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="4" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20">
+        <v>18</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="I20" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="J20" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="4" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21">
+        <v>19</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="I21" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="J21" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="2" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="2" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>21</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="2" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>22</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="4" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25">
+        <v>23</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="15" t="s">
+      <c r="J25" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="4" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26">
+        <v>24</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="H26" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I26" t="s">
         <v>22</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="J26" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="2" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>25</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="2" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>27</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="4" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29">
+        <v>29</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="I29" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="16" t="s">
+      <c r="J29" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30">
+        <v>31</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="I30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="J30" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31">
+        <v>33</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="I31" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="J31" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="2" t="s">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>35</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="G32" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C33" s="4"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C34" s="4"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C35" s="4"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C36" s="4"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C37" s="4"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C38" s="4"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C39" s="4"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C40" s="4"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C41" s="4"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C42" s="4"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C43" s="4"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C44" s="4"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C45" s="4"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="H1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
